--- a/references_sulphate.xlsx
+++ b/references_sulphate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Lab/Samples/DC fitlers/Orbitrap/2410_DC-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Paper/Data/DC HSO4/DC-2011-2_HSO4_M0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA04FEE-110B-4A4E-AA9E-2BEE8A439714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7350BF7-809F-DB4F-BF6A-1087ABD8D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22820" yWindow="-11220" windowWidth="22680" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,87 +36,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>sample_name</t>
   </si>
   <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>mean_d33S</t>
-  </si>
-  <si>
-    <t>mean_d34S</t>
-  </si>
-  <si>
-    <t>mean_d17O</t>
-  </si>
-  <si>
-    <t>mean_d18O</t>
-  </si>
-  <si>
-    <t>mean_d33S/34S</t>
-  </si>
-  <si>
-    <t>mean_d17O/34S</t>
-  </si>
-  <si>
-    <t>mean_d18O/34S</t>
-  </si>
-  <si>
-    <t>mean_d36S/34S</t>
-  </si>
-  <si>
-    <t>mean_d33S18O/34S</t>
-  </si>
-  <si>
-    <t>mean_d34S17O/34S</t>
-  </si>
-  <si>
-    <t>mean_d18O18O/34S</t>
-  </si>
-  <si>
-    <t>err_d33S</t>
-  </si>
-  <si>
     <t>err_d34S</t>
   </si>
   <si>
-    <t>err_d17O</t>
-  </si>
-  <si>
     <t>err_d18O</t>
   </si>
   <si>
-    <t>err_d33S/34S</t>
-  </si>
-  <si>
-    <t>err_d17O/34S</t>
-  </si>
-  <si>
-    <t>err_d18O/34S</t>
-  </si>
-  <si>
-    <t>err_d36S/34S</t>
-  </si>
-  <si>
-    <t>err_d33S18O/34S</t>
-  </si>
-  <si>
-    <t>err_d34S17O/34S</t>
-  </si>
-  <si>
-    <t>err_d18O18O/34S</t>
-  </si>
-  <si>
-    <t>err_d18O34S/34S</t>
-  </si>
-  <si>
-    <t>mean_d18O34S/34S</t>
+    <t>d34S</t>
+  </si>
+  <si>
+    <t>D33S</t>
+  </si>
+  <si>
+    <t>D17O</t>
+  </si>
+  <si>
+    <t>err_D33S</t>
+  </si>
+  <si>
+    <t>err_D17O</t>
+  </si>
+  <si>
+    <t>d18O</t>
+  </si>
+  <si>
+    <t>Sulf-Epsilon</t>
+  </si>
+  <si>
+    <t>Sulf-Alpha</t>
+  </si>
+  <si>
+    <t>Sulf-Beta</t>
+  </si>
+  <si>
+    <t>SMIF1</t>
+  </si>
+  <si>
+    <t>SMIF2</t>
+  </si>
+  <si>
+    <t>SodSul4</t>
+  </si>
+  <si>
+    <t>SodSul8</t>
+  </si>
+  <si>
+    <t>D34S18O</t>
+  </si>
+  <si>
+    <t>D33S18O</t>
+  </si>
+  <si>
+    <t>D34S17O</t>
+  </si>
+  <si>
+    <t>D18O18O</t>
+  </si>
+  <si>
+    <t>err_D34S18O</t>
+  </si>
+  <si>
+    <t>err_D33S18O</t>
+  </si>
+  <si>
+    <t>err_D34S17O</t>
+  </si>
+  <si>
+    <t>err_D18O18O</t>
+  </si>
+  <si>
+    <t>err_D36S</t>
+  </si>
+  <si>
+    <t>D36S</t>
   </si>
 </sst>
 </file>
@@ -493,339 +490,443 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="12" width="18.1640625" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" customWidth="1"/>
-    <col min="14" max="15" width="11" customWidth="1"/>
-    <col min="16" max="17" width="11.5" customWidth="1"/>
-    <col min="18" max="21" width="14.5" customWidth="1"/>
-    <col min="22" max="24" width="18.1640625" customWidth="1"/>
-    <col min="25" max="25" width="18.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B2" s="2">
+        <v>9.5380000000000003</v>
+      </c>
+      <c r="C2" s="2">
+        <v>10.262</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>14.81</v>
-      </c>
-      <c r="C2" s="1">
-        <v>10.262</v>
-      </c>
-      <c r="D2">
-        <v>3.57</v>
-      </c>
-      <c r="E2">
-        <v>0.52</v>
-      </c>
-      <c r="F2" s="1">
-        <f>1000*((B2+1000)/(C2+1000)-1)</f>
-        <v>4.5018025027170339</v>
-      </c>
-      <c r="G2" s="1">
-        <f>1000*((D2+1000)/(C2+1000)-1)</f>
-        <v>-6.6240242630128954</v>
-      </c>
-      <c r="H2" s="1">
-        <f>1000*((E2+1000)/(C2+1000)-1)</f>
-        <v>-9.6430430917919807</v>
-      </c>
-      <c r="I2" s="1">
-        <v>9.1818000000000008</v>
-      </c>
-      <c r="J2">
-        <f>E2</f>
-        <v>0.52</v>
-      </c>
-      <c r="K2" s="1">
-        <f>((1000+B2)*(1000+H2)/1000)-1000</f>
-        <v>5.0241434400186336</v>
-      </c>
-      <c r="L2" s="1">
-        <f>D2</f>
-        <v>3.57</v>
-      </c>
-      <c r="M2" s="1">
-        <f>((1000+H2)*(1000+E2)/1000)-1000</f>
-        <v>-9.1280574741996361</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="P2">
-        <v>0.6</v>
-      </c>
-      <c r="Q2">
-        <v>0.36</v>
-      </c>
-      <c r="R2" s="1">
-        <f>SQRT(N2^2+O2^2)</f>
-        <v>0.26627053911388693</v>
-      </c>
-      <c r="S2" s="1">
-        <f>SQRT(P2^2+O2^2)</f>
-        <v>0.63906181234681825</v>
-      </c>
-      <c r="T2" s="1">
-        <f>SQRT(Q2^2+O2^2)</f>
-        <v>0.42190046219457972</v>
-      </c>
-      <c r="U2" s="1">
-        <f>SQRT(0.35^2+O2^2)</f>
-        <v>0.41340053217188777</v>
-      </c>
-      <c r="V2">
-        <f>Q2</f>
-        <v>0.36</v>
-      </c>
-      <c r="W2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="X2" s="1">
-        <f>P2</f>
-        <v>0.6</v>
-      </c>
-      <c r="Y2" s="1">
-        <f>((1000+T2)*(1000+Q2)/1000)-1000</f>
-        <v>0.78205234636095611</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>22.417999999999999</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2">
+        <v>11.388999999999999</v>
+      </c>
+      <c r="C3" s="2">
         <v>21.527999999999999</v>
       </c>
-      <c r="D3" s="2">
-        <v>4.83</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2">
         <v>2.94</v>
       </c>
-      <c r="F3" s="1">
-        <f>1000*((B3+1000)/(C3+1000)-1)</f>
-        <v>0.87124386213588423</v>
-      </c>
-      <c r="G3" s="1">
-        <f>1000*((D3+1000)/(C3+1000)-1)</f>
-        <v>-16.346101134770642</v>
-      </c>
-      <c r="H3" s="1">
-        <f>1000*((E3+1000)/(C3+1000)-1)</f>
-        <v>-18.196270684699755</v>
-      </c>
-      <c r="I3" s="1">
-        <v>18.988199999999999</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="O3" s="1">
+      <c r="F3" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G3" s="2">
         <v>0.26</v>
       </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-0.32900000000000001</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
       <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-9.6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
         <v>0.5</v>
       </c>
-      <c r="Q3" s="2">
-        <v>0.23</v>
-      </c>
-      <c r="R3" s="1">
-        <f>SQRT(N3^2+O3^2)</f>
-        <v>0.32202484376209239</v>
-      </c>
-      <c r="S3" s="1">
-        <f>SQRT(P3^2+O3^2)</f>
-        <v>0.56356011214421486</v>
-      </c>
-      <c r="T3" s="1">
-        <f>SQRT(Q3^2+O3^2)</f>
-        <v>0.34713109915419565</v>
-      </c>
-      <c r="U3" s="1">
-        <f>SQRT(0.46^2+O3^2)</f>
-        <v>0.52839379254491625</v>
-      </c>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
+      <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
+      <c r="S10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/references_sulphate.xlsx
+++ b/references_sulphate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Paper/Data/DC HSO4/DC-2011-2_HSO4_M0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Lab/Orbitrap/Data treatment/DC-2011-HSO4-sep2B-newstds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7350BF7-809F-DB4F-BF6A-1087ABD8D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5BB7E8-B9FF-154A-8860-2363D30396D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22820" yWindow="-11220" windowWidth="22680" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-47940" yWindow="-2600" windowWidth="22680" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -570,9 +570,7 @@
         <v>10.262</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2">
-        <v>0.52</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2">
         <v>0.09</v>
       </c>
@@ -625,9 +623,7 @@
         <v>21.527999999999999</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2">
-        <v>2.94</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2">
         <v>0.08</v>
       </c>
@@ -683,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="F4" s="2">
         <v>0.1</v>
@@ -695,7 +691,7 @@
         <v>0.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -738,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>12</v>
+        <v>11.98</v>
       </c>
       <c r="F5" s="2">
         <v>0.1</v>
@@ -750,7 +746,7 @@
         <v>0.1</v>
       </c>
       <c r="I5" s="2">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -790,7 +786,9 @@
       <c r="D6" s="2">
         <v>0.9</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <v>-7.16</v>
+      </c>
       <c r="F6" s="2">
         <v>0.1</v>
       </c>
@@ -798,7 +796,9 @@
       <c r="H6" s="2">
         <v>0.1</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2">
+        <v>0.6</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2">
@@ -836,11 +836,17 @@
       <c r="D7" s="2">
         <v>2</v>
       </c>
+      <c r="E7" s="2">
+        <v>-6.78</v>
+      </c>
       <c r="F7" s="2">
         <v>0.1</v>
       </c>
       <c r="H7" s="2">
         <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1.1000000000000001</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -880,7 +886,9 @@
       <c r="D8" s="2">
         <v>7</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2">
+        <v>-6.71</v>
+      </c>
       <c r="F8" s="2">
         <v>0.1</v>
       </c>
@@ -888,7 +896,9 @@
       <c r="H8" s="2">
         <v>0.1</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="2">
+        <v>1.2</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2">

--- a/references_sulphate.xlsx
+++ b/references_sulphate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksaville/Documents/Lab/Orbitrap/Data treatment/DC-2011-HSO4-sep2B-newstds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5BB7E8-B9FF-154A-8860-2363D30396D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0B719B-114C-F542-88F3-EE74B93C4611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-47940" yWindow="-2600" windowWidth="22680" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10660" windowHeight="16300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -578,9 +578,7 @@
         <v>0.22</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="2">
-        <v>0.36</v>
-      </c>
+      <c r="I2" s="2"/>
       <c r="J2" s="2">
         <v>-0.14399999999999999</v>
       </c>
@@ -631,9 +629,7 @@
         <v>0.26</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2">
-        <v>0.23</v>
-      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2">
         <v>-0.32900000000000001</v>
       </c>
